--- a/output/stock_quant_scores/AAPL_income_df.xlsx
+++ b/output/stock_quant_scores/AAPL_income_df.xlsx
@@ -1118,7 +1118,9 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>111852000000</v>
+      </c>
       <c r="J6" t="n">
         <v>890000000</v>
       </c>
@@ -1135,10 +1137,14 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>5.67</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>94680000000</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1158,9 +1164,13 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>152836000000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>365817000000</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
     </row>
   </sheetData>
